--- a/data/Supplementary_Table_S1_Hyperparameters.xlsx
+++ b/data/Supplementary_Table_S1_Hyperparameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrar\PycharmProjects\ciliopathyP1\ciliopathy_family_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CC9DFF-4EA8-4F26-B680-658CA5EE2D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB351D3-E858-4433-B649-BEE0C76E8F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplementary Table S1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="57">
   <si>
     <t>Model</t>
   </si>
@@ -58,85 +58,91 @@
     <t>[200, 500]</t>
   </si>
   <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>GridSearchCV</t>
+  </si>
+  <si>
+    <t>4-fold stratified CV</t>
+  </si>
+  <si>
+    <t>f1_weighted</t>
+  </si>
+  <si>
+    <t>max_depth</t>
+  </si>
+  <si>
+    <t>[None, 10, 20]</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>min_samples_split</t>
+  </si>
+  <si>
+    <t>[2, 5]</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>min_samples_leaf</t>
+  </si>
+  <si>
+    <t>[1, 2]</t>
+  </si>
+  <si>
+    <t>max_features</t>
+  </si>
+  <si>
+    <t>[sqrt, log2]</t>
+  </si>
+  <si>
+    <t>sqrt</t>
+  </si>
+  <si>
+    <t>Fixed before training</t>
+  </si>
+  <si>
+    <t>random_state</t>
+  </si>
+  <si>
+    <t>Fixed, not tuned</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Preset</t>
+  </si>
+  <si>
+    <t>class_weight</t>
+  </si>
+  <si>
+    <t>balanced</t>
+  </si>
+  <si>
+    <t>n_jobs</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>[200, 400]</t>
+  </si>
+  <si>
     <t>200</t>
   </si>
   <si>
-    <t>GridSearchCV</t>
-  </si>
-  <si>
-    <t>5-fold stratified CV</t>
-  </si>
-  <si>
-    <t>f1_weighted</t>
-  </si>
-  <si>
-    <t>max_depth</t>
-  </si>
-  <si>
-    <t>[None, 10, 20]</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>min_samples_split</t>
-  </si>
-  <si>
-    <t>[2, 5]</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>min_samples_leaf</t>
-  </si>
-  <si>
-    <t>[1, 2]</t>
-  </si>
-  <si>
-    <t>max_features</t>
-  </si>
-  <si>
-    <t>[sqrt, log2]</t>
-  </si>
-  <si>
-    <t>log2</t>
-  </si>
-  <si>
-    <t>Fixed before training</t>
-  </si>
-  <si>
-    <t>random_state</t>
-  </si>
-  <si>
-    <t>Fixed, not tuned</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>Preset</t>
-  </si>
-  <si>
-    <t>class_weight</t>
-  </si>
-  <si>
-    <t>balanced</t>
-  </si>
-  <si>
-    <t>n_jobs</t>
-  </si>
-  <si>
-    <t>-1</t>
-  </si>
-  <si>
-    <t>XGBoost</t>
-  </si>
-  <si>
-    <t>[200, 400]</t>
-  </si>
-  <si>
-    <t>400</t>
+    <t>[3, 5, 7]</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>learning_rate</t>
@@ -145,7 +151,7 @@
     <t>[0.03, 0.1]</t>
   </si>
   <si>
-    <t>0.03</t>
+    <t>0.1</t>
   </si>
   <si>
     <t>subsample</t>
@@ -154,15 +160,12 @@
     <t>[0.8, 1.0]</t>
   </si>
   <si>
-    <t>1.0</t>
+    <t>0.8</t>
   </si>
   <si>
     <t>colsample_bytree</t>
   </si>
   <si>
-    <t>0.8</t>
-  </si>
-  <si>
     <t>objective</t>
   </si>
   <si>
@@ -178,13 +181,16 @@
     <t>num_class</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>[3, 5, 7]</t>
-  </si>
-  <si>
-    <t>s</t>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>sample_weight</t>
+  </si>
+  <si>
+    <t>balanced (compute_sample_weight('balanced'))</t>
   </si>
 </sst>
 </file>
@@ -569,8 +575,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -582,7 +588,7 @@
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -634,7 +640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -660,7 +666,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -686,7 +692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -699,8 +705,8 @@
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2">
-        <v>2</v>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -712,7 +718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -738,7 +744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -751,20 +757,20 @@
       <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -777,20 +783,20 @@
       <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -803,20 +809,20 @@
       <c r="D9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
@@ -842,7 +848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -853,10 +859,10 @@
         <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -868,7 +874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -876,13 +882,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -894,7 +900,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -902,13 +908,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -920,7 +926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
@@ -928,10 +934,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>46</v>
@@ -946,7 +952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>36</v>
       </c>
@@ -959,20 +965,20 @@
       <c r="D15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>36</v>
       </c>
@@ -980,25 +986,25 @@
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>48</v>
+      <c r="E16" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>36</v>
       </c>
@@ -1006,25 +1012,25 @@
         <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>50</v>
+      <c r="E17" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>36</v>
       </c>
@@ -1032,25 +1038,25 @@
         <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>52</v>
+      <c r="E18" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -1063,22 +1069,43 @@
       <c r="D19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>35</v>
+      <c r="E19" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E23" t="s">
-        <v>54</v>
+    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
